--- a/templates/spreadsheets/performance-ratios-template.xlsx
+++ b/templates/spreadsheets/performance-ratios-template.xlsx
@@ -741,13 +741,13 @@
     <t>See:</t>
   </si>
   <si>
-    <t>docs/templates/spec-template.md (repo-level)</t>
+    <t>templates/spec-template.md (repo-level)</t>
   </si>
   <si>
     <t>Course:</t>
   </si>
   <si>
-    <t>courses/BUS-629-VEMBA-International-Corporate-Finance/</t>
+    <t>courses/International-Corporate-Finance/</t>
   </si>
   <si>
     <t>Prepared per UH Mānoa brand standards (docs/_branding/design.json). Primary green #024731 · Open Sans typography · ADA-compliant contrast.</t>

--- a/templates/spreadsheets/performance-ratios-template.xlsx
+++ b/templates/spreadsheets/performance-ratios-template.xlsx
@@ -687,10 +687,10 @@
     <t>Prefix / Pattern</t>
   </si>
   <si>
-    <t>BAL_[item]_[yr]</t>
-  </si>
-  <si>
-    <t>Balance-sheet line items, suffixed with fiscal year (e.g., BAL_assets_total_2024).</t>
+    <t>BAL_[item]_curr, BAL_[item]_prior</t>
+  </si>
+  <si>
+    <t>Balance-sheet line items, suffixed _curr for the current year or _prior for the prior year (e.g., BAL_assets_total_curr).</t>
   </si>
   <si>
     <t>INC_[item]</t>
